--- a/medford_datchiki_dlya_uzi.xlsx
+++ b/medford_datchiki_dlya_uzi.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Датчики для УЗИ для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов GE, SonoScape, Siemens, Mindray, Samsung, Chison, Canon — всего 20 позиций.</t>
+          <t>Датчики для УЗИ для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов GE, SonoScape, Siemens, Mindray, Samsung, Chison, Canon.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_datchiki_dlya_uzi.xlsx
+++ b/medford_datchiki_dlya_uzi.xlsx
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать датчики для УЗИ для клиники?</t>
+          <t>Какие существуют виды датчиков для УЗИ?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Количество элементов, Диапазон частот, МГц, Радиус кривизны, мм, Размер апертуры, мм). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Основные типы — линейные (5–18 МГц) для поверхностных органов, сосудов и щитовидной железы; конвексные (2–7,5 МГц) для брюшной полости и акушерства; секторные фазированные (1–5 МГц) для эхокардиографии; внутриполостные (5–10 МГц) для трансвагинальных и трансректальных исследований. Отдельно выделяют объёмные 3D/4D и карандашные датчики.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Как работает датчик УЗИ?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Внутри датчика расположены пьезоэлементы, которые под электрическим импульсом излучают ультразвук, а затем принимают отражённое от тканей эхо и преобразуют его обратно в электрический сигнал. Аппарат строит из этих сигналов изображение. Частота и геометрия решётки задают глубину проникновения и область обзора.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Как выбрать датчик под аппарат?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены GE, SonoScape, Siemens, Mindray, Samsung, Chison, Canon. Подберём модель под ваши задачи, совместимость и бюджет.</t>
+          <t>Отталкивайтесь от двух условий: тип исследования и совместимость с платформой. Датчик рассчитан на конкретную марку и модель сканера и определённый разъём, поэтому уточните точное наименование аппарата. Затем подберите тип (линейный, конвексный, секторный, внутриполостной) и частотный диапазон под задачи кабинета.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Чем отличается монокристаллический датчик?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>Монокристаллические датчики (например, Mindray SP5-1N, Samsung PM1-6A) используют пьезоматериал из выращенного монокристалла вместо обычной керамики. Это расширяет полосу рабочих частот и повышает чувствительность, что улучшает детализацию и проникновение. Их применяют там, где важно качество изображения на разных глубинах.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Какой датчик нужен для УЗИ малого таза?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Для трансабдоминального УЗИ малого таза применяют конвексный датчик, для трансвагинального и трансректального — внутриполостной с частотой около 5–10 МГц. Внутриполостной подводится вплотную к органу и даёт высокое разрешение. Конкретную методику и датчик выбирает врач исходя из клинической задачи.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Какие существуют виды датчиков для УЗИ?</t>
+          <t>Можно ли ставить датчик от другого бренда?</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Нет, без подтверждённой совместимости. Датчик проектируется под конкретную платформу с определённым разъёмом и протоколом обмена. Датчик GE не подойдёт к аппарату Siemens или Mindray. Перед покупкой сверьте марку, модель сканера и тип коннектора, иначе датчик не распознается системой.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит аппарат для УЗИ?</t>
+          <t>Что проверить при покупке восстановленного датчика?</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Оцените целостность акустической линзы и корпуса, отсутствие трещин, состояние кабеля и контактов разъёма, а также равномерность изображения без выпадающих элементов (тёмных полос). Уточните, проходил ли датчик проверку и какие режимы обработки допустимы. Для внутриполостных моделей важна корректная дезинфекция.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Датчики для УЗИ для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов GE, SonoScape, Siemens, Mindray, Samsung, Chison, Canon.</t>
+          <t>Датчики для УЗИ — сменные ультразвуковые преобразователи, которые формируют и принимают эхосигнал и определяют, какие органы можно исследовать на сканере. В категории представлены линейные, конвексные, секторные фазированные, объёмные 3D/4D и внутриполостные датчики брендов GE, Siemens, Samsung, Mindray, Canon, SonoScape и Chison. Диапазон рабочих частот моделей — от 1 МГц (секторные Siemens 4V1) до 13 МГц (внутриполостной SonoScape VE9-5), число элементов — от 64 до 192, встречаются монокристаллические и матричные конструкции. Тип датчика подбирают под область исследования и совместимость с конкретной моделью УЗ-аппарата.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>Основные типы датчиков УЗИ</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое датчики для УЗИ</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -4546,251 +4546,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — Основные типы датчиков УЗИ</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Модель</t>
+          <t>Тип датчика</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>Диапазон частот</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Количество элементов</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Диапазон частот, МГц</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Радиус кривизны, мм</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Размер апертуры, мм</t>
+          <t>Область применения</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Секторный фазированный датчик GE S4-10-D</t>
+          <t>Линейный</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>5–18 МГц</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>3-9</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Поверхностные органы, сосуды, щитовидная железа, суставы</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Конвексный широкополосный датчик SonoScape 3C-A</t>
+          <t>Конвексный</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>SonoScape</t>
+          <t>2–7,5 МГц</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>1,0-6,0</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Брюшная полость, акушерство</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Siemens 6C2 конвексный датчик УЗИ</t>
+          <t>Секторный фазированный</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>1–5 МГц</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>2-6</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Эхокардиография, сердце</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Siemens 10V4 секторный датчик УЗИ</t>
+          <t>Внутриполостной</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>5–10 МГц</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>4,1-9,9</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>13.056</t>
+          <t>Трансвагинальные и трансректальные исследования</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Вагинально-ректальный датчик SonoScape 6V3</t>
+          <t>Объёмный 3D/4D</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>SonoScape</t>
+          <t>2–8 МГц</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>4.0–11.0</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Внутриполостной датчик УЗИ Sonoscape 6V5A</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>SonoScape</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>4,0-9,0</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Акушерство, гинекология, объёмная реконструкция</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4802,7 +4677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5128,12 +5003,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Определите область исследования</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается датчики для УЗИ: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Тип датчика диктуется задачей: поверхностные структуры и сосуды — линейный, брюшная полость и акушерство — конвексный, сердце — секторный фазированный, малый таз и предстательная железа — внутриполостной. С этого шага начинается любой подбор.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -5173,12 +5048,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Сопоставьте частоту и глубину</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Высокая частота даёт детализацию, но малую глубину; низкая — наоборот. Линейные работают в 5–18 МГц для поверхностных органов, конвексные в 2–7,5 МГц для глубоких, секторные в 1–5 МГц для сердца. В каталоге диапазон моделей — от 1 до 13 МГц.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -5218,12 +5093,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Проверьте совместимость с аппаратом</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Количество элементов, Диапазон частот, МГц, Радиус кривизны, мм, Размер апертуры, мм. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Датчик рассчитан на конкретную платформу: важны марка, модель сканера и тип разъёма. Датчик GE, Siemens, Samsung или Mindray не заработает на чужой системе без совместимости. Уточните точное наименование вашего аппарата до заказа.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -5263,12 +5138,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Оцените число элементов и конструкцию</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость. В каталоге: GE, SonoScape, Siemens, Mindray, Samsung, Chison, Canon.</t>
+          <t>Число пьезоэлементов влияет на разрешение: в каталоге модели с 64–192 элементами. Монокристаллические (Mindray SP5-1N, Samsung PM1-6A) и матричные конструкции дают шире полосу частот и чувствительность. Сопоставьте это с классом задач кабинета.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -5308,12 +5183,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Учтите специальные форматы</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Для акушерства и гинекологии берут объёмные 3D/4D датчики (GE RAB6-RS, Samsung CV1-8AD), для кардиологии — карандашный (Samsung DP8B) под непрерывноволновую допплерографию. Подбирайте формат под методики, которые реально применяет клиника.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -5353,12 +5228,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Проверьте состояние и обработку</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Датчик — хрупкий узел: линза, кабель и разъём чувствительны к ударам и перегибам. При покупке восстановленного датчика оцените целостность элементов и отсутствие выпадающих кристаллов. Уточните допустимые режимы дезинфекции, особенно для внутриполостных моделей.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -5408,7 +5283,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Датчики для УЗИ подбирают под задачи отделения и совместимость с имеющимся оборудованием. В нашем каталоге представлены GE, SonoScape, Siemens, Mindray, Samsung, Chison, Canon. При выборе обращают внимание на количество элементов, диапазон частот, радиус кривизны, размер апертуры, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>Датчик подбирают по двум осям: тип исследования и совместимость с платформой аппарата. Для сосудов и щитовидной железы нужен высокочастотный линейный датчик, для брюшной полости и акушерства — конвексный на 2–7,5 МГц, для эхокардиографии — секторный фазированный на 1–5 МГц. Монокристаллические модели, как Mindray SP5-1N или Samsung PM1-6A, дают шире полосу частот и чувствительность. Всегда сверяйте марку и модель аппарата и тип разъёма — датчик от другой платформы не заработает.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -5692,13 +5567,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое датчики для УЗИ</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Датчики для УЗИ — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели брендов GE, SonoScape, Siemens, Mindray, Samsung, Chison, Canon. Подберём вариант под задачи вашего отделения.</t>
+          <t>Датчик УЗИ — сменный преобразователь, задающий рабочую частоту, глубину и область исследования на сканере. Основные типы: линейные (5–18 МГц, поверхностные органы, сосуды, щитовидная железа), конвексные (2–7,5 МГц, брюшная полость, акушерство), секторные фазированные (1–5 МГц, кардиология) и внутриполостные (5–10 МГц, трансвагинальные и трансректальные исследования). Отдельно выделяют объёмные 3D/4D и карандашные датчики. В каталоге — модели GE, Siemens, Samsung, Mindray, Canon, SonoScape и Chison; датчик подбирают по типу исследования и совместимости с конкретным аппаратом.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -5735,13 +5610,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Что такое датчик УЗИ</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Количество элементов, Диапазон частот, МГц, Радиус кривизны, мм, Размер апертуры, мм), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>Датчик УЗИ — сменный преобразователь, который излучает ультразвук и принимает отражённое эхо, формируя изображение на сканере. Именно датчик определяет, какие органы можно исследовать, на какой глубине и с каким разрешением. Тип, частотный диапазон и число элементов подбирают под область исследования и совместимость с моделью аппарата.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -5778,13 +5653,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Основные типы датчиков</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>Линейные датчики (5–18 МГц) сканируют поверхностные органы, сосуды, щитовидную железу и суставы. Конвексные (2–7,5 МГц) — брюшную полость и акушерство. Секторные фазированные (1–5 МГц) — сердце. Внутриполостные (5–10 МГц) — органы малого таза при трансвагинальном и трансректальном доступе. Объёмные 3D/4D добавляют трёхмерную реконструкцию.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -5821,13 +5696,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>От чего зависит качество изображения</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>На детализацию влияют рабочая частота, число пьезоэлементов и материал преобразователя. Высокая частота даёт разрешение на малой глубине, низкая — проникновение вглубь. Монокристаллические и матричные конструкции расширяют полосу частот и чувствительность. В каталоге — датчики с 64–192 элементами и диапазоном от 1 до 13 МГц.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -5844,6 +5719,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Как подобрать датчик под клинику</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Сначала уточните точную марку и модель УЗ-аппарата и тип разъёма — датчик работает только на совместимой платформе. Затем выберите тип и частотный диапазон под методики кабинета: сосудистые, абдоминальные, кардиологические или внутриполостные исследования. В каталоге представлены GE, Siemens, Samsung, Mindray, Canon, SonoScape и Chison.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>datchiki_dlya_uzi</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
